--- a/outputs/daily/hr_rankings_2026-07-14.xlsx
+++ b/outputs/daily/hr_rankings_2026-07-14.xlsx
@@ -844,28 +844,32 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr"/>
-      <c r="X2" t="inlineStr"/>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="Y2" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>RotoWire parsed no lineups; not found on RotoWire</t>
-        </is>
-      </c>
+      <c r="AB2" t="inlineStr"/>
       <c r="AC2" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -1140,28 +1144,32 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr"/>
-      <c r="X3" t="inlineStr"/>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="Y3" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>RotoWire parsed no lineups; not found on RotoWire</t>
-        </is>
-      </c>
+      <c r="AB3" t="inlineStr"/>
       <c r="AC3" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -1436,28 +1444,32 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr"/>
-      <c r="X4" t="inlineStr"/>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="Y4" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>RotoWire parsed no lineups; not found on RotoWire</t>
-        </is>
-      </c>
+      <c r="AB4" t="inlineStr"/>
       <c r="AC4" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -1732,28 +1744,32 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr"/>
-      <c r="X5" t="inlineStr"/>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="Y5" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>RotoWire parsed no lineups; not found on RotoWire</t>
-        </is>
-      </c>
+      <c r="AB5" t="inlineStr"/>
       <c r="AC5" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -2028,28 +2044,32 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="W6" t="inlineStr"/>
-      <c r="X6" t="inlineStr"/>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="Y6" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>RotoWire parsed no lineups; not found on RotoWire</t>
-        </is>
-      </c>
+      <c r="AB6" t="inlineStr"/>
       <c r="AC6" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -2324,28 +2344,32 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="W7" t="inlineStr"/>
-      <c r="X7" t="inlineStr"/>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="Y7" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>RotoWire parsed no lineups; not found on RotoWire</t>
-        </is>
-      </c>
+      <c r="AB7" t="inlineStr"/>
       <c r="AC7" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -2620,28 +2644,32 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="W8" t="inlineStr"/>
-      <c r="X8" t="inlineStr"/>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="Y8" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>RotoWire parsed no lineups; not found on RotoWire</t>
-        </is>
-      </c>
+      <c r="AB8" t="inlineStr"/>
       <c r="AC8" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -2916,28 +2944,32 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="W9" t="inlineStr"/>
-      <c r="X9" t="inlineStr"/>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="Y9" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>RotoWire parsed no lineups; not found on RotoWire</t>
-        </is>
-      </c>
+      <c r="AB9" t="inlineStr"/>
       <c r="AC9" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -3212,28 +3244,32 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="W10" t="inlineStr"/>
-      <c r="X10" t="inlineStr"/>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
       <c r="Y10" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>RotoWire parsed no lineups; not found on RotoWire</t>
-        </is>
-      </c>
+      <c r="AB10" t="inlineStr"/>
       <c r="AC10" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -3508,28 +3544,32 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="W11" t="inlineStr"/>
-      <c r="X11" t="inlineStr"/>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="Y11" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>RotoWire parsed no lineups; not found on RotoWire</t>
-        </is>
-      </c>
+      <c r="AB11" t="inlineStr"/>
       <c r="AC11" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -3804,28 +3844,32 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="W12" t="inlineStr"/>
-      <c r="X12" t="inlineStr"/>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="Y12" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>RotoWire parsed no lineups; not found on RotoWire</t>
-        </is>
-      </c>
+      <c r="AB12" t="inlineStr"/>
       <c r="AC12" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -4100,28 +4144,32 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="W13" t="inlineStr"/>
-      <c r="X13" t="inlineStr"/>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="Y13" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>RotoWire parsed no lineups; not found on RotoWire</t>
-        </is>
-      </c>
+      <c r="AB13" t="inlineStr"/>
       <c r="AC13" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -4396,28 +4444,32 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="W14" t="inlineStr"/>
-      <c r="X14" t="inlineStr"/>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
       <c r="Y14" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>RotoWire parsed no lineups; not found on RotoWire</t>
-        </is>
-      </c>
+      <c r="AB14" t="inlineStr"/>
       <c r="AC14" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -4692,28 +4744,32 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="W15" t="inlineStr"/>
-      <c r="X15" t="inlineStr"/>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="Y15" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>RotoWire parsed no lineups; not found on RotoWire</t>
-        </is>
-      </c>
+      <c r="AB15" t="inlineStr"/>
       <c r="AC15" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -4988,28 +5044,32 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="W16" t="inlineStr"/>
-      <c r="X16" t="inlineStr"/>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="Y16" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>RotoWire parsed no lineups; not found on RotoWire</t>
-        </is>
-      </c>
+      <c r="AB16" t="inlineStr"/>
       <c r="AC16" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -5284,28 +5344,32 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="W17" t="inlineStr"/>
-      <c r="X17" t="inlineStr"/>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
       <c r="Y17" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>RotoWire parsed no lineups; not found on RotoWire</t>
-        </is>
-      </c>
+      <c r="AB17" t="inlineStr"/>
       <c r="AC17" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -5580,28 +5644,32 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="W18" t="inlineStr"/>
-      <c r="X18" t="inlineStr"/>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="Y18" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>RotoWire parsed no lineups; not found on RotoWire</t>
-        </is>
-      </c>
+      <c r="AB18" t="inlineStr"/>
       <c r="AC18" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -5876,28 +5944,32 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="W19" t="inlineStr"/>
-      <c r="X19" t="inlineStr"/>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
       <c r="Y19" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>RotoWire parsed no lineups; not found on RotoWire</t>
-        </is>
-      </c>
+      <c r="AB19" t="inlineStr"/>
       <c r="AC19" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -6518,28 +6590,32 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr"/>
-      <c r="X2" t="inlineStr"/>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="Y2" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>RotoWire parsed no lineups; not found on RotoWire</t>
-        </is>
-      </c>
+      <c r="AB2" t="inlineStr"/>
       <c r="AC2" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -6814,28 +6890,32 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr"/>
-      <c r="X3" t="inlineStr"/>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="Y3" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>RotoWire parsed no lineups; not found on RotoWire</t>
-        </is>
-      </c>
+      <c r="AB3" t="inlineStr"/>
       <c r="AC3" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -7110,28 +7190,32 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr"/>
-      <c r="X4" t="inlineStr"/>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="Y4" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>RotoWire parsed no lineups; not found on RotoWire</t>
-        </is>
-      </c>
+      <c r="AB4" t="inlineStr"/>
       <c r="AC4" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -7406,28 +7490,32 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr"/>
-      <c r="X5" t="inlineStr"/>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="Y5" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>RotoWire parsed no lineups; not found on RotoWire</t>
-        </is>
-      </c>
+      <c r="AB5" t="inlineStr"/>
       <c r="AC5" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -7702,28 +7790,32 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="W6" t="inlineStr"/>
-      <c r="X6" t="inlineStr"/>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="Y6" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>RotoWire parsed no lineups; not found on RotoWire</t>
-        </is>
-      </c>
+      <c r="AB6" t="inlineStr"/>
       <c r="AC6" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -7998,28 +8090,32 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="W7" t="inlineStr"/>
-      <c r="X7" t="inlineStr"/>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="Y7" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>RotoWire parsed no lineups; not found on RotoWire</t>
-        </is>
-      </c>
+      <c r="AB7" t="inlineStr"/>
       <c r="AC7" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -8294,28 +8390,32 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="W8" t="inlineStr"/>
-      <c r="X8" t="inlineStr"/>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="Y8" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>RotoWire parsed no lineups; not found on RotoWire</t>
-        </is>
-      </c>
+      <c r="AB8" t="inlineStr"/>
       <c r="AC8" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -8590,28 +8690,32 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="W9" t="inlineStr"/>
-      <c r="X9" t="inlineStr"/>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="Y9" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>RotoWire parsed no lineups; not found on RotoWire</t>
-        </is>
-      </c>
+      <c r="AB9" t="inlineStr"/>
       <c r="AC9" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -8886,28 +8990,32 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="W10" t="inlineStr"/>
-      <c r="X10" t="inlineStr"/>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
       <c r="Y10" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>RotoWire parsed no lineups; not found on RotoWire</t>
-        </is>
-      </c>
+      <c r="AB10" t="inlineStr"/>
       <c r="AC10" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -9182,28 +9290,32 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="W11" t="inlineStr"/>
-      <c r="X11" t="inlineStr"/>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="Y11" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>RotoWire parsed no lineups; not found on RotoWire</t>
-        </is>
-      </c>
+      <c r="AB11" t="inlineStr"/>
       <c r="AC11" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -9478,28 +9590,32 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="W12" t="inlineStr"/>
-      <c r="X12" t="inlineStr"/>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="Y12" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>RotoWire parsed no lineups; not found on RotoWire</t>
-        </is>
-      </c>
+      <c r="AB12" t="inlineStr"/>
       <c r="AC12" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -9774,28 +9890,32 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="W13" t="inlineStr"/>
-      <c r="X13" t="inlineStr"/>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="Y13" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>RotoWire parsed no lineups; not found on RotoWire</t>
-        </is>
-      </c>
+      <c r="AB13" t="inlineStr"/>
       <c r="AC13" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -10070,28 +10190,32 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="W14" t="inlineStr"/>
-      <c r="X14" t="inlineStr"/>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
       <c r="Y14" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>RotoWire parsed no lineups; not found on RotoWire</t>
-        </is>
-      </c>
+      <c r="AB14" t="inlineStr"/>
       <c r="AC14" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -10366,28 +10490,32 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="W15" t="inlineStr"/>
-      <c r="X15" t="inlineStr"/>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="Y15" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>RotoWire parsed no lineups; not found on RotoWire</t>
-        </is>
-      </c>
+      <c r="AB15" t="inlineStr"/>
       <c r="AC15" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -10662,28 +10790,32 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="W16" t="inlineStr"/>
-      <c r="X16" t="inlineStr"/>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="Y16" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>RotoWire parsed no lineups; not found on RotoWire</t>
-        </is>
-      </c>
+      <c r="AB16" t="inlineStr"/>
       <c r="AC16" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -10958,28 +11090,32 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="W17" t="inlineStr"/>
-      <c r="X17" t="inlineStr"/>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
       <c r="Y17" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>RotoWire parsed no lineups; not found on RotoWire</t>
-        </is>
-      </c>
+      <c r="AB17" t="inlineStr"/>
       <c r="AC17" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -11254,28 +11390,32 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="W18" t="inlineStr"/>
-      <c r="X18" t="inlineStr"/>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="Y18" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>RotoWire parsed no lineups; not found on RotoWire</t>
-        </is>
-      </c>
+      <c r="AB18" t="inlineStr"/>
       <c r="AC18" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -11550,28 +11690,32 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="W19" t="inlineStr"/>
-      <c r="X19" t="inlineStr"/>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
       <c r="Y19" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>RotoWire parsed no lineups; not found on RotoWire</t>
-        </is>
-      </c>
+      <c r="AB19" t="inlineStr"/>
       <c r="AC19" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>

--- a/outputs/daily/hr_rankings_2026-07-14.xlsx
+++ b/outputs/daily/hr_rankings_2026-07-14.xlsx
@@ -780,7 +780,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -804,7 +804,7 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>67.2</v>
+        <v>69.3</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -818,7 +818,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>Elite Power, Strong Barrel, Premium Lineup Spot</t>
+          <t>Elite Power, Strong Barrel, Good Environment, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P2" t="n">
@@ -828,7 +828,7 @@
         <v>35.9</v>
       </c>
       <c r="R2" t="n">
-        <v>60.8</v>
+        <v>75.3</v>
       </c>
       <c r="S2" t="n">
         <v>100</v>
@@ -1014,7 +1014,7 @@
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
@@ -1029,7 +1029,7 @@
       </c>
       <c r="BJ2" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>68</t>
         </is>
       </c>
       <c r="BK2" t="inlineStr">
@@ -1039,7 +1039,7 @@
       </c>
       <c r="BL2" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>82</t>
         </is>
       </c>
       <c r="BM2" t="inlineStr">
@@ -1080,7 +1080,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -1104,7 +1104,7 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>65.7</v>
+        <v>67.8</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -1118,7 +1118,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge, Hot Hitter/Streak</t>
+          <t>Strong Barrel, Good Environment, Premium Lineup Spot, Platoon Edge, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P3" t="n">
@@ -1128,7 +1128,7 @@
         <v>35.9</v>
       </c>
       <c r="R3" t="n">
-        <v>60.8</v>
+        <v>75.3</v>
       </c>
       <c r="S3" t="n">
         <v>93.2</v>
@@ -1314,7 +1314,7 @@
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BH3" t="inlineStr">
@@ -1329,7 +1329,7 @@
       </c>
       <c r="BJ3" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>68</t>
         </is>
       </c>
       <c r="BK3" t="inlineStr">
@@ -1339,7 +1339,7 @@
       </c>
       <c r="BL3" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>82</t>
         </is>
       </c>
       <c r="BM3" t="inlineStr">
@@ -1380,7 +1380,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -1404,7 +1404,7 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>63.5</v>
+        <v>65.7</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -1418,7 +1418,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Elite Power, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Elite Power, Strong Barrel, Good Environment, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P4" t="n">
@@ -1428,7 +1428,7 @@
         <v>18.2</v>
       </c>
       <c r="R4" t="n">
-        <v>60.8</v>
+        <v>75.3</v>
       </c>
       <c r="S4" t="n">
         <v>93.2</v>
@@ -1614,7 +1614,7 @@
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
@@ -1629,7 +1629,7 @@
       </c>
       <c r="BJ4" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>68</t>
         </is>
       </c>
       <c r="BK4" t="inlineStr">
@@ -1639,7 +1639,7 @@
       </c>
       <c r="BL4" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>82</t>
         </is>
       </c>
       <c r="BM4" t="inlineStr">
@@ -1680,7 +1680,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1704,7 +1704,7 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>62.2</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -1718,7 +1718,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Good Environment, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P5" t="n">
@@ -1728,7 +1728,7 @@
         <v>18.2</v>
       </c>
       <c r="R5" t="n">
-        <v>60.8</v>
+        <v>75.3</v>
       </c>
       <c r="S5" t="n">
         <v>100</v>
@@ -1914,7 +1914,7 @@
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
@@ -1929,7 +1929,7 @@
       </c>
       <c r="BJ5" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>68</t>
         </is>
       </c>
       <c r="BK5" t="inlineStr">
@@ -1939,7 +1939,7 @@
       </c>
       <c r="BL5" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>82</t>
         </is>
       </c>
       <c r="BM5" t="inlineStr">
@@ -1980,7 +1980,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -2004,7 +2004,7 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>61.4</v>
+        <v>63.6</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Good Environment, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P6" t="n">
@@ -2028,7 +2028,7 @@
         <v>35.9</v>
       </c>
       <c r="R6" t="n">
-        <v>60.8</v>
+        <v>75.3</v>
       </c>
       <c r="S6" t="n">
         <v>94.90000000000001</v>
@@ -2214,7 +2214,7 @@
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BH6" t="inlineStr">
@@ -2229,7 +2229,7 @@
       </c>
       <c r="BJ6" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>68</t>
         </is>
       </c>
       <c r="BK6" t="inlineStr">
@@ -2239,7 +2239,7 @@
       </c>
       <c r="BL6" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>82</t>
         </is>
       </c>
       <c r="BM6" t="inlineStr">
@@ -2280,7 +2280,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -2304,11 +2304,11 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>58.4</v>
+        <v>60.6</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>Longshot</t>
+          <t>Tier 3</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -2318,7 +2318,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Good Environment, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P7" t="n">
@@ -2328,7 +2328,7 @@
         <v>35.9</v>
       </c>
       <c r="R7" t="n">
-        <v>60.8</v>
+        <v>75.3</v>
       </c>
       <c r="S7" t="n">
         <v>96.59999999999999</v>
@@ -2514,7 +2514,7 @@
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BH7" t="inlineStr">
@@ -2529,7 +2529,7 @@
       </c>
       <c r="BJ7" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>68</t>
         </is>
       </c>
       <c r="BK7" t="inlineStr">
@@ -2539,7 +2539,7 @@
       </c>
       <c r="BL7" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>82</t>
         </is>
       </c>
       <c r="BM7" t="inlineStr">
@@ -2580,7 +2580,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -2604,11 +2604,11 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>58</v>
+        <v>60.2</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>Longshot</t>
+          <t>Tier 3</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Strong Barrel, Platoon Edge</t>
+          <t>Strong Barrel, Good Environment, Platoon Edge</t>
         </is>
       </c>
       <c r="P8" t="n">
@@ -2628,7 +2628,7 @@
         <v>35.9</v>
       </c>
       <c r="R8" t="n">
-        <v>60.8</v>
+        <v>75.3</v>
       </c>
       <c r="S8" t="n">
         <v>86.40000000000001</v>
@@ -2814,7 +2814,7 @@
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BH8" t="inlineStr">
@@ -2829,7 +2829,7 @@
       </c>
       <c r="BJ8" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>68</t>
         </is>
       </c>
       <c r="BK8" t="inlineStr">
@@ -2839,7 +2839,7 @@
       </c>
       <c r="BL8" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>82</t>
         </is>
       </c>
       <c r="BM8" t="inlineStr">
@@ -2880,7 +2880,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -2904,7 +2904,7 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>57.6</v>
+        <v>59.8</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -2918,7 +2918,7 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Strong Barrel, Hot Hitter/Streak</t>
+          <t>Strong Barrel, Good Environment, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P9" t="n">
@@ -2928,7 +2928,7 @@
         <v>35.9</v>
       </c>
       <c r="R9" t="n">
-        <v>60.8</v>
+        <v>75.3</v>
       </c>
       <c r="S9" t="n">
         <v>64.3</v>
@@ -3114,7 +3114,7 @@
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BH9" t="inlineStr">
@@ -3129,7 +3129,7 @@
       </c>
       <c r="BJ9" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>68</t>
         </is>
       </c>
       <c r="BK9" t="inlineStr">
@@ -3139,7 +3139,7 @@
       </c>
       <c r="BL9" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>82</t>
         </is>
       </c>
       <c r="BM9" t="inlineStr">
@@ -3180,7 +3180,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -3204,7 +3204,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>51.8</v>
+        <v>54</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -3218,7 +3218,7 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Strong Barrel</t>
+          <t>Strong Barrel, Good Environment</t>
         </is>
       </c>
       <c r="P10" t="n">
@@ -3228,7 +3228,7 @@
         <v>35.9</v>
       </c>
       <c r="R10" t="n">
-        <v>60.8</v>
+        <v>75.3</v>
       </c>
       <c r="S10" t="n">
         <v>52.4</v>
@@ -3414,7 +3414,7 @@
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BH10" t="inlineStr">
@@ -3429,7 +3429,7 @@
       </c>
       <c r="BJ10" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>68</t>
         </is>
       </c>
       <c r="BK10" t="inlineStr">
@@ -3439,7 +3439,7 @@
       </c>
       <c r="BL10" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>82</t>
         </is>
       </c>
       <c r="BM10" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -3504,7 +3504,7 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>51.5</v>
+        <v>53.7</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -3518,7 +3518,7 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Strong Barrel, Platoon Edge</t>
+          <t>Strong Barrel, Good Environment, Platoon Edge</t>
         </is>
       </c>
       <c r="P11" t="n">
@@ -3528,7 +3528,7 @@
         <v>18.2</v>
       </c>
       <c r="R11" t="n">
-        <v>60.8</v>
+        <v>75.3</v>
       </c>
       <c r="S11" t="n">
         <v>86.40000000000001</v>
@@ -3714,7 +3714,7 @@
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BH11" t="inlineStr">
@@ -3729,7 +3729,7 @@
       </c>
       <c r="BJ11" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>68</t>
         </is>
       </c>
       <c r="BK11" t="inlineStr">
@@ -3739,7 +3739,7 @@
       </c>
       <c r="BL11" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>82</t>
         </is>
       </c>
       <c r="BM11" t="inlineStr">
@@ -3780,7 +3780,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -3804,7 +3804,7 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>50.6</v>
+        <v>52.7</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -3818,7 +3818,7 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Good Environment, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P12" t="n">
@@ -3828,7 +3828,7 @@
         <v>18.2</v>
       </c>
       <c r="R12" t="n">
-        <v>60.8</v>
+        <v>75.3</v>
       </c>
       <c r="S12" t="n">
         <v>96.59999999999999</v>
@@ -4014,7 +4014,7 @@
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BH12" t="inlineStr">
@@ -4029,7 +4029,7 @@
       </c>
       <c r="BJ12" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>68</t>
         </is>
       </c>
       <c r="BK12" t="inlineStr">
@@ -4039,7 +4039,7 @@
       </c>
       <c r="BL12" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>82</t>
         </is>
       </c>
       <c r="BM12" t="inlineStr">
@@ -4080,7 +4080,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -4104,7 +4104,7 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>50.5</v>
+        <v>52.6</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -4118,7 +4118,7 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Premium Lineup Spot, Platoon Edge, Hot Hitter/Streak</t>
+          <t>Good Environment, Premium Lineup Spot, Platoon Edge, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P13" t="n">
@@ -4128,7 +4128,7 @@
         <v>18.2</v>
       </c>
       <c r="R13" t="n">
-        <v>60.8</v>
+        <v>75.3</v>
       </c>
       <c r="S13" t="n">
         <v>94.90000000000001</v>
@@ -4314,7 +4314,7 @@
       </c>
       <c r="BG13" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BH13" t="inlineStr">
@@ -4329,7 +4329,7 @@
       </c>
       <c r="BJ13" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>68</t>
         </is>
       </c>
       <c r="BK13" t="inlineStr">
@@ -4339,7 +4339,7 @@
       </c>
       <c r="BL13" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>82</t>
         </is>
       </c>
       <c r="BM13" t="inlineStr">
@@ -4380,7 +4380,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -4404,7 +4404,7 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>47.9</v>
+        <v>50</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -4418,7 +4418,7 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Strong Barrel, Platoon Edge</t>
+          <t>Strong Barrel, Good Environment, Platoon Edge</t>
         </is>
       </c>
       <c r="P14" t="n">
@@ -4428,7 +4428,7 @@
         <v>18.2</v>
       </c>
       <c r="R14" t="n">
-        <v>60.8</v>
+        <v>75.3</v>
       </c>
       <c r="S14" t="n">
         <v>44.8</v>
@@ -4614,7 +4614,7 @@
       </c>
       <c r="BG14" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BH14" t="inlineStr">
@@ -4629,7 +4629,7 @@
       </c>
       <c r="BJ14" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>68</t>
         </is>
       </c>
       <c r="BK14" t="inlineStr">
@@ -4639,7 +4639,7 @@
       </c>
       <c r="BL14" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>82</t>
         </is>
       </c>
       <c r="BM14" t="inlineStr">
@@ -4680,7 +4680,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -4704,7 +4704,7 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>44.2</v>
+        <v>46.4</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -4718,7 +4718,7 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>No major boost</t>
+          <t>Good Environment</t>
         </is>
       </c>
       <c r="P15" t="n">
@@ -4728,7 +4728,7 @@
         <v>35.9</v>
       </c>
       <c r="R15" t="n">
-        <v>60.8</v>
+        <v>75.3</v>
       </c>
       <c r="S15" t="n">
         <v>76.2</v>
@@ -4914,7 +4914,7 @@
       </c>
       <c r="BG15" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BH15" t="inlineStr">
@@ -4929,7 +4929,7 @@
       </c>
       <c r="BJ15" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>68</t>
         </is>
       </c>
       <c r="BK15" t="inlineStr">
@@ -4939,7 +4939,7 @@
       </c>
       <c r="BL15" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>82</t>
         </is>
       </c>
       <c r="BM15" t="inlineStr">
@@ -4980,7 +4980,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -5004,7 +5004,7 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>43.6</v>
+        <v>45.7</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -5018,7 +5018,7 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>Platoon Edge</t>
+          <t>Good Environment, Platoon Edge</t>
         </is>
       </c>
       <c r="P16" t="n">
@@ -5028,7 +5028,7 @@
         <v>18.2</v>
       </c>
       <c r="R16" t="n">
-        <v>60.8</v>
+        <v>75.3</v>
       </c>
       <c r="S16" t="n">
         <v>64.3</v>
@@ -5214,7 +5214,7 @@
       </c>
       <c r="BG16" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BH16" t="inlineStr">
@@ -5229,7 +5229,7 @@
       </c>
       <c r="BJ16" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>68</t>
         </is>
       </c>
       <c r="BK16" t="inlineStr">
@@ -5239,7 +5239,7 @@
       </c>
       <c r="BL16" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>82</t>
         </is>
       </c>
       <c r="BM16" t="inlineStr">
@@ -5280,7 +5280,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -5304,7 +5304,7 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>40.3</v>
+        <v>42.5</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -5318,7 +5318,7 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>No major boost</t>
+          <t>Good Environment</t>
         </is>
       </c>
       <c r="P17" t="n">
@@ -5328,7 +5328,7 @@
         <v>18.2</v>
       </c>
       <c r="R17" t="n">
-        <v>60.8</v>
+        <v>75.3</v>
       </c>
       <c r="S17" t="n">
         <v>52.4</v>
@@ -5514,7 +5514,7 @@
       </c>
       <c r="BG17" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BH17" t="inlineStr">
@@ -5529,7 +5529,7 @@
       </c>
       <c r="BJ17" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>68</t>
         </is>
       </c>
       <c r="BK17" t="inlineStr">
@@ -5539,7 +5539,7 @@
       </c>
       <c r="BL17" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>82</t>
         </is>
       </c>
       <c r="BM17" t="inlineStr">
@@ -5580,7 +5580,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -5604,7 +5604,7 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>36.9</v>
+        <v>39.1</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
@@ -5618,7 +5618,7 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>Platoon Edge</t>
+          <t>Good Environment, Platoon Edge</t>
         </is>
       </c>
       <c r="P18" t="n">
@@ -5628,7 +5628,7 @@
         <v>17.2</v>
       </c>
       <c r="R18" t="n">
-        <v>60.8</v>
+        <v>75.3</v>
       </c>
       <c r="S18" t="n">
         <v>76.2</v>
@@ -5814,7 +5814,7 @@
       </c>
       <c r="BG18" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BH18" t="inlineStr">
@@ -5829,7 +5829,7 @@
       </c>
       <c r="BJ18" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>68</t>
         </is>
       </c>
       <c r="BK18" t="inlineStr">
@@ -5839,7 +5839,7 @@
       </c>
       <c r="BL18" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>82</t>
         </is>
       </c>
       <c r="BM18" t="inlineStr">
@@ -5880,7 +5880,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -5904,7 +5904,7 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>35.7</v>
+        <v>37.9</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
@@ -5918,7 +5918,7 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>Platoon Edge</t>
+          <t>Good Environment, Platoon Edge</t>
         </is>
       </c>
       <c r="P19" t="n">
@@ -5928,7 +5928,7 @@
         <v>35.9</v>
       </c>
       <c r="R19" t="n">
-        <v>60.8</v>
+        <v>75.3</v>
       </c>
       <c r="S19" t="n">
         <v>44.8</v>
@@ -6114,7 +6114,7 @@
       </c>
       <c r="BG19" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BH19" t="inlineStr">
@@ -6129,7 +6129,7 @@
       </c>
       <c r="BJ19" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>68</t>
         </is>
       </c>
       <c r="BK19" t="inlineStr">
@@ -6139,7 +6139,7 @@
       </c>
       <c r="BL19" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>82</t>
         </is>
       </c>
       <c r="BM19" t="inlineStr">
@@ -6526,7 +6526,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -6550,7 +6550,7 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>67.2</v>
+        <v>69.3</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -6564,7 +6564,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>Elite Power, Strong Barrel, Premium Lineup Spot</t>
+          <t>Elite Power, Strong Barrel, Good Environment, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P2" t="n">
@@ -6574,7 +6574,7 @@
         <v>35.9</v>
       </c>
       <c r="R2" t="n">
-        <v>60.8</v>
+        <v>75.3</v>
       </c>
       <c r="S2" t="n">
         <v>100</v>
@@ -6760,7 +6760,7 @@
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
@@ -6775,7 +6775,7 @@
       </c>
       <c r="BJ2" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>68</t>
         </is>
       </c>
       <c r="BK2" t="inlineStr">
@@ -6785,7 +6785,7 @@
       </c>
       <c r="BL2" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>82</t>
         </is>
       </c>
       <c r="BM2" t="inlineStr">
@@ -6826,7 +6826,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -6850,7 +6850,7 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>65.7</v>
+        <v>67.8</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -6864,7 +6864,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge, Hot Hitter/Streak</t>
+          <t>Strong Barrel, Good Environment, Premium Lineup Spot, Platoon Edge, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P3" t="n">
@@ -6874,7 +6874,7 @@
         <v>35.9</v>
       </c>
       <c r="R3" t="n">
-        <v>60.8</v>
+        <v>75.3</v>
       </c>
       <c r="S3" t="n">
         <v>93.2</v>
@@ -7060,7 +7060,7 @@
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BH3" t="inlineStr">
@@ -7075,7 +7075,7 @@
       </c>
       <c r="BJ3" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>68</t>
         </is>
       </c>
       <c r="BK3" t="inlineStr">
@@ -7085,7 +7085,7 @@
       </c>
       <c r="BL3" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>82</t>
         </is>
       </c>
       <c r="BM3" t="inlineStr">
@@ -7126,7 +7126,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -7150,7 +7150,7 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>63.5</v>
+        <v>65.7</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -7164,7 +7164,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Elite Power, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Elite Power, Strong Barrel, Good Environment, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P4" t="n">
@@ -7174,7 +7174,7 @@
         <v>18.2</v>
       </c>
       <c r="R4" t="n">
-        <v>60.8</v>
+        <v>75.3</v>
       </c>
       <c r="S4" t="n">
         <v>93.2</v>
@@ -7360,7 +7360,7 @@
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
@@ -7375,7 +7375,7 @@
       </c>
       <c r="BJ4" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>68</t>
         </is>
       </c>
       <c r="BK4" t="inlineStr">
@@ -7385,7 +7385,7 @@
       </c>
       <c r="BL4" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>82</t>
         </is>
       </c>
       <c r="BM4" t="inlineStr">
@@ -7426,7 +7426,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -7450,7 +7450,7 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>62.2</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -7464,7 +7464,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Good Environment, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P5" t="n">
@@ -7474,7 +7474,7 @@
         <v>18.2</v>
       </c>
       <c r="R5" t="n">
-        <v>60.8</v>
+        <v>75.3</v>
       </c>
       <c r="S5" t="n">
         <v>100</v>
@@ -7660,7 +7660,7 @@
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
@@ -7675,7 +7675,7 @@
       </c>
       <c r="BJ5" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>68</t>
         </is>
       </c>
       <c r="BK5" t="inlineStr">
@@ -7685,7 +7685,7 @@
       </c>
       <c r="BL5" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>82</t>
         </is>
       </c>
       <c r="BM5" t="inlineStr">
@@ -7726,7 +7726,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -7750,7 +7750,7 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>61.4</v>
+        <v>63.6</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -7764,7 +7764,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Good Environment, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P6" t="n">
@@ -7774,7 +7774,7 @@
         <v>35.9</v>
       </c>
       <c r="R6" t="n">
-        <v>60.8</v>
+        <v>75.3</v>
       </c>
       <c r="S6" t="n">
         <v>94.90000000000001</v>
@@ -7960,7 +7960,7 @@
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BH6" t="inlineStr">
@@ -7975,7 +7975,7 @@
       </c>
       <c r="BJ6" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>68</t>
         </is>
       </c>
       <c r="BK6" t="inlineStr">
@@ -7985,7 +7985,7 @@
       </c>
       <c r="BL6" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>82</t>
         </is>
       </c>
       <c r="BM6" t="inlineStr">
@@ -8026,7 +8026,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -8050,11 +8050,11 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>58.4</v>
+        <v>60.6</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>Longshot</t>
+          <t>Tier 3</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -8064,7 +8064,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Good Environment, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P7" t="n">
@@ -8074,7 +8074,7 @@
         <v>35.9</v>
       </c>
       <c r="R7" t="n">
-        <v>60.8</v>
+        <v>75.3</v>
       </c>
       <c r="S7" t="n">
         <v>96.59999999999999</v>
@@ -8260,7 +8260,7 @@
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BH7" t="inlineStr">
@@ -8275,7 +8275,7 @@
       </c>
       <c r="BJ7" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>68</t>
         </is>
       </c>
       <c r="BK7" t="inlineStr">
@@ -8285,7 +8285,7 @@
       </c>
       <c r="BL7" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>82</t>
         </is>
       </c>
       <c r="BM7" t="inlineStr">
@@ -8326,7 +8326,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -8350,11 +8350,11 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>58</v>
+        <v>60.2</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>Longshot</t>
+          <t>Tier 3</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -8364,7 +8364,7 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Strong Barrel, Platoon Edge</t>
+          <t>Strong Barrel, Good Environment, Platoon Edge</t>
         </is>
       </c>
       <c r="P8" t="n">
@@ -8374,7 +8374,7 @@
         <v>35.9</v>
       </c>
       <c r="R8" t="n">
-        <v>60.8</v>
+        <v>75.3</v>
       </c>
       <c r="S8" t="n">
         <v>86.40000000000001</v>
@@ -8560,7 +8560,7 @@
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BH8" t="inlineStr">
@@ -8575,7 +8575,7 @@
       </c>
       <c r="BJ8" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>68</t>
         </is>
       </c>
       <c r="BK8" t="inlineStr">
@@ -8585,7 +8585,7 @@
       </c>
       <c r="BL8" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>82</t>
         </is>
       </c>
       <c r="BM8" t="inlineStr">
@@ -8626,7 +8626,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -8650,7 +8650,7 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>57.6</v>
+        <v>59.8</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -8664,7 +8664,7 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Strong Barrel, Hot Hitter/Streak</t>
+          <t>Strong Barrel, Good Environment, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P9" t="n">
@@ -8674,7 +8674,7 @@
         <v>35.9</v>
       </c>
       <c r="R9" t="n">
-        <v>60.8</v>
+        <v>75.3</v>
       </c>
       <c r="S9" t="n">
         <v>64.3</v>
@@ -8860,7 +8860,7 @@
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BH9" t="inlineStr">
@@ -8875,7 +8875,7 @@
       </c>
       <c r="BJ9" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>68</t>
         </is>
       </c>
       <c r="BK9" t="inlineStr">
@@ -8885,7 +8885,7 @@
       </c>
       <c r="BL9" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>82</t>
         </is>
       </c>
       <c r="BM9" t="inlineStr">
@@ -8926,7 +8926,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -8950,7 +8950,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>51.8</v>
+        <v>54</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -8964,7 +8964,7 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Strong Barrel</t>
+          <t>Strong Barrel, Good Environment</t>
         </is>
       </c>
       <c r="P10" t="n">
@@ -8974,7 +8974,7 @@
         <v>35.9</v>
       </c>
       <c r="R10" t="n">
-        <v>60.8</v>
+        <v>75.3</v>
       </c>
       <c r="S10" t="n">
         <v>52.4</v>
@@ -9160,7 +9160,7 @@
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BH10" t="inlineStr">
@@ -9175,7 +9175,7 @@
       </c>
       <c r="BJ10" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>68</t>
         </is>
       </c>
       <c r="BK10" t="inlineStr">
@@ -9185,7 +9185,7 @@
       </c>
       <c r="BL10" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>82</t>
         </is>
       </c>
       <c r="BM10" t="inlineStr">
@@ -9226,7 +9226,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -9250,7 +9250,7 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>51.5</v>
+        <v>53.7</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -9264,7 +9264,7 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Strong Barrel, Platoon Edge</t>
+          <t>Strong Barrel, Good Environment, Platoon Edge</t>
         </is>
       </c>
       <c r="P11" t="n">
@@ -9274,7 +9274,7 @@
         <v>18.2</v>
       </c>
       <c r="R11" t="n">
-        <v>60.8</v>
+        <v>75.3</v>
       </c>
       <c r="S11" t="n">
         <v>86.40000000000001</v>
@@ -9460,7 +9460,7 @@
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BH11" t="inlineStr">
@@ -9475,7 +9475,7 @@
       </c>
       <c r="BJ11" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>68</t>
         </is>
       </c>
       <c r="BK11" t="inlineStr">
@@ -9485,7 +9485,7 @@
       </c>
       <c r="BL11" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>82</t>
         </is>
       </c>
       <c r="BM11" t="inlineStr">
@@ -9526,7 +9526,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -9550,7 +9550,7 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>50.6</v>
+        <v>52.7</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -9564,7 +9564,7 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Good Environment, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P12" t="n">
@@ -9574,7 +9574,7 @@
         <v>18.2</v>
       </c>
       <c r="R12" t="n">
-        <v>60.8</v>
+        <v>75.3</v>
       </c>
       <c r="S12" t="n">
         <v>96.59999999999999</v>
@@ -9760,7 +9760,7 @@
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BH12" t="inlineStr">
@@ -9775,7 +9775,7 @@
       </c>
       <c r="BJ12" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>68</t>
         </is>
       </c>
       <c r="BK12" t="inlineStr">
@@ -9785,7 +9785,7 @@
       </c>
       <c r="BL12" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>82</t>
         </is>
       </c>
       <c r="BM12" t="inlineStr">
@@ -9826,7 +9826,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -9850,7 +9850,7 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>50.5</v>
+        <v>52.6</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -9864,7 +9864,7 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Premium Lineup Spot, Platoon Edge, Hot Hitter/Streak</t>
+          <t>Good Environment, Premium Lineup Spot, Platoon Edge, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P13" t="n">
@@ -9874,7 +9874,7 @@
         <v>18.2</v>
       </c>
       <c r="R13" t="n">
-        <v>60.8</v>
+        <v>75.3</v>
       </c>
       <c r="S13" t="n">
         <v>94.90000000000001</v>
@@ -10060,7 +10060,7 @@
       </c>
       <c r="BG13" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BH13" t="inlineStr">
@@ -10075,7 +10075,7 @@
       </c>
       <c r="BJ13" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>68</t>
         </is>
       </c>
       <c r="BK13" t="inlineStr">
@@ -10085,7 +10085,7 @@
       </c>
       <c r="BL13" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>82</t>
         </is>
       </c>
       <c r="BM13" t="inlineStr">
@@ -10126,7 +10126,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -10150,7 +10150,7 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>47.9</v>
+        <v>50</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -10164,7 +10164,7 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Strong Barrel, Platoon Edge</t>
+          <t>Strong Barrel, Good Environment, Platoon Edge</t>
         </is>
       </c>
       <c r="P14" t="n">
@@ -10174,7 +10174,7 @@
         <v>18.2</v>
       </c>
       <c r="R14" t="n">
-        <v>60.8</v>
+        <v>75.3</v>
       </c>
       <c r="S14" t="n">
         <v>44.8</v>
@@ -10360,7 +10360,7 @@
       </c>
       <c r="BG14" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BH14" t="inlineStr">
@@ -10375,7 +10375,7 @@
       </c>
       <c r="BJ14" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>68</t>
         </is>
       </c>
       <c r="BK14" t="inlineStr">
@@ -10385,7 +10385,7 @@
       </c>
       <c r="BL14" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>82</t>
         </is>
       </c>
       <c r="BM14" t="inlineStr">
@@ -10426,7 +10426,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -10450,7 +10450,7 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>44.2</v>
+        <v>46.4</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -10464,7 +10464,7 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>No major boost</t>
+          <t>Good Environment</t>
         </is>
       </c>
       <c r="P15" t="n">
@@ -10474,7 +10474,7 @@
         <v>35.9</v>
       </c>
       <c r="R15" t="n">
-        <v>60.8</v>
+        <v>75.3</v>
       </c>
       <c r="S15" t="n">
         <v>76.2</v>
@@ -10660,7 +10660,7 @@
       </c>
       <c r="BG15" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BH15" t="inlineStr">
@@ -10675,7 +10675,7 @@
       </c>
       <c r="BJ15" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>68</t>
         </is>
       </c>
       <c r="BK15" t="inlineStr">
@@ -10685,7 +10685,7 @@
       </c>
       <c r="BL15" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>82</t>
         </is>
       </c>
       <c r="BM15" t="inlineStr">
@@ -10726,7 +10726,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -10750,7 +10750,7 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>43.6</v>
+        <v>45.7</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -10764,7 +10764,7 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>Platoon Edge</t>
+          <t>Good Environment, Platoon Edge</t>
         </is>
       </c>
       <c r="P16" t="n">
@@ -10774,7 +10774,7 @@
         <v>18.2</v>
       </c>
       <c r="R16" t="n">
-        <v>60.8</v>
+        <v>75.3</v>
       </c>
       <c r="S16" t="n">
         <v>64.3</v>
@@ -10960,7 +10960,7 @@
       </c>
       <c r="BG16" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BH16" t="inlineStr">
@@ -10975,7 +10975,7 @@
       </c>
       <c r="BJ16" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>68</t>
         </is>
       </c>
       <c r="BK16" t="inlineStr">
@@ -10985,7 +10985,7 @@
       </c>
       <c r="BL16" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>82</t>
         </is>
       </c>
       <c r="BM16" t="inlineStr">
@@ -11026,7 +11026,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -11050,7 +11050,7 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>40.3</v>
+        <v>42.5</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -11064,7 +11064,7 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>No major boost</t>
+          <t>Good Environment</t>
         </is>
       </c>
       <c r="P17" t="n">
@@ -11074,7 +11074,7 @@
         <v>18.2</v>
       </c>
       <c r="R17" t="n">
-        <v>60.8</v>
+        <v>75.3</v>
       </c>
       <c r="S17" t="n">
         <v>52.4</v>
@@ -11260,7 +11260,7 @@
       </c>
       <c r="BG17" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BH17" t="inlineStr">
@@ -11275,7 +11275,7 @@
       </c>
       <c r="BJ17" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>68</t>
         </is>
       </c>
       <c r="BK17" t="inlineStr">
@@ -11285,7 +11285,7 @@
       </c>
       <c r="BL17" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>82</t>
         </is>
       </c>
       <c r="BM17" t="inlineStr">
@@ -11326,7 +11326,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -11350,7 +11350,7 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>36.9</v>
+        <v>39.1</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
@@ -11364,7 +11364,7 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>Platoon Edge</t>
+          <t>Good Environment, Platoon Edge</t>
         </is>
       </c>
       <c r="P18" t="n">
@@ -11374,7 +11374,7 @@
         <v>17.2</v>
       </c>
       <c r="R18" t="n">
-        <v>60.8</v>
+        <v>75.3</v>
       </c>
       <c r="S18" t="n">
         <v>76.2</v>
@@ -11560,7 +11560,7 @@
       </c>
       <c r="BG18" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BH18" t="inlineStr">
@@ -11575,7 +11575,7 @@
       </c>
       <c r="BJ18" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>68</t>
         </is>
       </c>
       <c r="BK18" t="inlineStr">
@@ -11585,7 +11585,7 @@
       </c>
       <c r="BL18" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>82</t>
         </is>
       </c>
       <c r="BM18" t="inlineStr">
@@ -11626,7 +11626,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -11650,7 +11650,7 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>35.7</v>
+        <v>37.9</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
@@ -11664,7 +11664,7 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>Platoon Edge</t>
+          <t>Good Environment, Platoon Edge</t>
         </is>
       </c>
       <c r="P19" t="n">
@@ -11674,7 +11674,7 @@
         <v>35.9</v>
       </c>
       <c r="R19" t="n">
-        <v>60.8</v>
+        <v>75.3</v>
       </c>
       <c r="S19" t="n">
         <v>44.8</v>
@@ -11860,7 +11860,7 @@
       </c>
       <c r="BG19" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BH19" t="inlineStr">
@@ -11875,7 +11875,7 @@
       </c>
       <c r="BJ19" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>68</t>
         </is>
       </c>
       <c r="BK19" t="inlineStr">
@@ -11885,7 +11885,7 @@
       </c>
       <c r="BL19" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>82</t>
         </is>
       </c>
       <c r="BM19" t="inlineStr">
